--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -1699,17 +1699,24 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>1096</v>
+        <v>1153</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>1714</v>
-      </c>
-      <c r="E47" s="4" t="n"/>
+        <v>1839</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>2095</v>
+      </c>
       <c r="F47" s="4" t="n"/>
       <c r="G47" s="4" t="n"/>
       <c r="H47" s="8" t="n"/>
       <c r="I47" s="6" t="n"/>
       <c r="J47" s="9" t="n"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>상향1차</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2631,6 +2631,27 @@
       </c>
       <c r="E83" t="n">
         <v>300</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>420770</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>344</v>
+      </c>
+      <c r="D84" t="n">
+        <v>955</v>
+      </c>
+      <c r="E84" t="n">
+        <v>840</v>
       </c>
     </row>
   </sheetData>

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>1153</v>
+        <v>1139</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>1839</v>
+        <v>1744</v>
       </c>
       <c r="E47" s="4" t="n">
         <v>2095</v>
@@ -1711,7 +1711,11 @@
       <c r="G47" s="4" t="n"/>
       <c r="H47" s="8" t="n"/>
       <c r="I47" s="6" t="n"/>
-      <c r="J47" s="9" t="n"/>
+      <c r="J47" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>상향1차</t>

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>1896</v>
+        <v>2583</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>3175</v>
+        <v>4385</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>3971</v>
+        <v>5658</v>
       </c>
       <c r="F40" s="4" t="n"/>
       <c r="G40" s="4" t="n"/>
@@ -1523,8 +1523,10 @@
           <t>회사/증권사 컨센서스</t>
         </is>
       </c>
-      <c r="J40" s="9" t="n">
-        <v>46218</v>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -2359,19 +2359,23 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>1723</v>
+        <v>1897</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>2116</v>
+        <v>2325</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>2463</v>
+        <v>2393</v>
       </c>
       <c r="F72" s="4" t="n"/>
       <c r="G72" s="4" t="n"/>
       <c r="H72" s="8" t="n"/>
       <c r="I72" s="6" t="n"/>
-      <c r="J72" s="9" t="n"/>
+      <c r="J72" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -991,22 +991,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>네패스</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>033640</t>
+          <t>420770</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>411</v>
+        <v>344</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>522</v>
+        <v>955</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>620</v>
+        <v>840</v>
       </c>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
@@ -1017,22 +1017,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>네패스아크</t>
+          <t>네패스</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>330860</t>
+          <t>033640</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>269</v>
+        <v>411</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>442</v>
+        <v>522</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>589</v>
+        <v>620</v>
       </c>
       <c r="F21" s="4" t="n"/>
       <c r="G21" s="4" t="n"/>
@@ -1043,74 +1043,80 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>대덕전자</t>
+          <t>네패스아크</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>353200</t>
+          <t>330860</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2759</v>
+        <v>269</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>4081</v>
+        <v>442</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>5068</v>
+        <v>589</v>
       </c>
       <c r="F22" s="4" t="n"/>
       <c r="G22" s="4" t="n"/>
       <c r="H22" s="8" t="n"/>
       <c r="I22" s="6" t="n"/>
       <c r="J22" s="9" t="n"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>8/4 추정치 상향</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>대덕전자</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>353200</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>8775</v>
+        <v>2759</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>20815</v>
+        <v>4081</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>24999</v>
+        <v>5068</v>
       </c>
       <c r="F23" s="4" t="n"/>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="8" t="n"/>
       <c r="I23" s="6" t="n"/>
       <c r="J23" s="9" t="n"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>8/4 추정치 상향</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>005290</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
+          <t>003490</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>8775</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>20815</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>24999</v>
+      </c>
       <c r="F24" s="4" t="n"/>
       <c r="G24" s="4" t="n"/>
       <c r="H24" s="8" t="n"/>
@@ -1120,23 +1126,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>131970</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>484</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>1131</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>1335</v>
-      </c>
+          <t>005290</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="n"/>
       <c r="G25" s="4" t="n"/>
       <c r="H25" s="8" t="n"/>
@@ -1146,22 +1146,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>디아이</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>003160</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>967</v>
+        <v>484</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1151</v>
+        <v>1131</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1241</v>
+        <v>1335</v>
       </c>
       <c r="F26" s="4" t="n"/>
       <c r="G26" s="4" t="n"/>
@@ -1172,17 +1172,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>디아이티</t>
+          <t>디아이</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>110990</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
+          <t>003160</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>967</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>1151</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>1241</v>
+      </c>
       <c r="F27" s="4" t="n"/>
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="8" t="n"/>
@@ -1192,12 +1198,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>디엔에프</t>
+          <t>디아이티</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>092070</t>
+          <t>110990</t>
         </is>
       </c>
       <c r="C28" s="4" t="n"/>
@@ -1212,20 +1218,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>디케이티</t>
+          <t>디엔에프</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>290550</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>313</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>568</v>
-      </c>
+          <t>092070</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
       <c r="E29" s="4" t="n"/>
       <c r="F29" s="4" t="n"/>
       <c r="G29" s="4" t="n"/>
@@ -1236,23 +1238,21 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>롯데관광개발</t>
+          <t>디케이티</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>032350</t>
+          <t>290550</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1995</v>
+        <v>313</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2425</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>2685</v>
-      </c>
+        <v>568</v>
+      </c>
+      <c r="E30" s="4" t="n"/>
       <c r="F30" s="4" t="n"/>
       <c r="G30" s="4" t="n"/>
       <c r="H30" s="8" t="n"/>
@@ -1262,22 +1262,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>롯데관광개발</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>032350</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>965</v>
+        <v>1995</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1357</v>
+        <v>2425</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1554</v>
+        <v>2685</v>
       </c>
       <c r="F31" s="4" t="n"/>
       <c r="G31" s="4" t="n"/>
@@ -1288,22 +1288,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>비씨엔씨</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>146320</t>
+          <t>089970</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>93</v>
+        <v>965</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>162</v>
+        <v>1357</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>219</v>
+        <v>1554</v>
       </c>
       <c r="F32" s="4" t="n"/>
       <c r="G32" s="4" t="n"/>
@@ -1314,22 +1314,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>비에이치</t>
+          <t>비씨엔씨</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>090460</t>
+          <t>146320</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1148</v>
+        <v>93</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1429</v>
+        <v>162</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1607</v>
+        <v>219</v>
       </c>
       <c r="F33" s="4" t="n"/>
       <c r="G33" s="4" t="n"/>
@@ -1340,22 +1340,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>비에이치</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>090460</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1201</v>
+        <v>1148</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1522</v>
+        <v>1429</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1928</v>
+        <v>1607</v>
       </c>
       <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
@@ -1366,22 +1366,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2517</v>
+        <v>1201</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>3337</v>
+        <v>1522</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>4247</v>
+        <v>1928</v>
       </c>
       <c r="F35" s="4" t="n"/>
       <c r="G35" s="4" t="n"/>
@@ -1392,22 +1392,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>319</v>
+        <v>2517</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>427</v>
+        <v>3337</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>486</v>
+        <v>4247</v>
       </c>
       <c r="F36" s="4" t="n"/>
       <c r="G36" s="4" t="n"/>
@@ -1418,22 +1418,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>세진중공업</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>075580</t>
+          <t>252990</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>861</v>
+        <v>319</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>1010</v>
+        <v>427</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1056</v>
+        <v>486</v>
       </c>
       <c r="F37" s="4" t="n"/>
       <c r="G37" s="4" t="n"/>
@@ -1444,22 +1444,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>솔브레인</t>
+          <t>세진중공업</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>357780</t>
+          <t>075580</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>1941</v>
+        <v>861</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>2518</v>
+        <v>1010</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>3133</v>
+        <v>1056</v>
       </c>
       <c r="F38" s="4" t="n"/>
       <c r="G38" s="4" t="n"/>
@@ -1470,22 +1470,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>솔브레인</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>357780</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>2750</v>
+        <v>1941</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>3532</v>
+        <v>2518</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>4124</v>
+        <v>3133</v>
       </c>
       <c r="F39" s="4" t="n"/>
       <c r="G39" s="4" t="n"/>
@@ -1496,81 +1496,85 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>2583</v>
+        <v>2750</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>4385</v>
+        <v>3532</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>5658</v>
+        <v>4124</v>
       </c>
       <c r="F40" s="4" t="n"/>
       <c r="G40" s="4" t="n"/>
-      <c r="H40" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>회사/증권사 컨센서스</t>
-        </is>
-      </c>
-      <c r="J40" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>예시값 - 실제 컨센서스로 수정</t>
-        </is>
-      </c>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="6" t="n"/>
+      <c r="J40" s="9" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>싸이맥스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>160980</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>260</v>
+        <v>2583</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>450</v>
-      </c>
-      <c r="E41" s="4" t="n"/>
+        <v>4385</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>5658</v>
+      </c>
       <c r="F41" s="4" t="n"/>
       <c r="G41" s="4" t="n"/>
-      <c r="H41" s="8" t="n"/>
-      <c r="I41" s="6" t="n"/>
-      <c r="J41" s="9" t="n"/>
+      <c r="H41" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>회사/증권사 컨센서스</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>46302</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>예시값 - 실제 컨센서스로 수정</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>에스앤에스텍</t>
+          <t>싸이맥스</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>101490</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="n"/>
+          <t>160980</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>260</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>450</v>
+      </c>
       <c r="E42" s="4" t="n"/>
       <c r="F42" s="4" t="n"/>
       <c r="G42" s="4" t="n"/>
@@ -1581,23 +1585,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>에스티아이</t>
+          <t>에스앤에스텍</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>039440</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>751</v>
-      </c>
-      <c r="D43" s="4" t="n">
-        <v>1306</v>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>1341</v>
-      </c>
+          <t>101490</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
       <c r="F43" s="4" t="n"/>
       <c r="G43" s="4" t="n"/>
       <c r="H43" s="8" t="n"/>
@@ -1607,21 +1605,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>에스티아이</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>039440</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>231</v>
+        <v>751</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>371</v>
-      </c>
-      <c r="E44" s="4" t="n"/>
+        <v>1306</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>1341</v>
+      </c>
       <c r="F44" s="4" t="n"/>
       <c r="G44" s="4" t="n"/>
       <c r="H44" s="8" t="n"/>
@@ -1631,19 +1631,19 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>엑시콘</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>092870</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>148</v>
+        <v>231</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>282</v>
+        <v>371</v>
       </c>
       <c r="E45" s="4" t="n"/>
       <c r="F45" s="4" t="n"/>
@@ -1655,120 +1655,116 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>엑시콘</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>092870</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>734</v>
+        <v>148</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>1174</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>1545</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="E46" s="4" t="n"/>
       <c r="F46" s="4" t="n"/>
       <c r="G46" s="4" t="n"/>
       <c r="H46" s="8" t="n"/>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">컨센서스 </t>
-        </is>
-      </c>
-      <c r="J46" s="9" t="n">
-        <v>46254</v>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>상향 650&gt;734(1회)</t>
-        </is>
-      </c>
+      <c r="I46" s="6" t="n"/>
+      <c r="J46" s="9" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>033160</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>1139</v>
+        <v>734</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>1744</v>
+        <v>1174</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>2095</v>
+        <v>1545</v>
       </c>
       <c r="F47" s="4" t="n"/>
       <c r="G47" s="4" t="n"/>
       <c r="H47" s="8" t="n"/>
-      <c r="I47" s="6" t="n"/>
-      <c r="J47" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">컨센서스 </t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>46254</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>상향1차</t>
+          <t>상향 650&gt;734(1회)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>와이씨</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>232140</t>
+          <t>033160</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>545</v>
+        <v>1139</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>726</v>
+        <v>1744</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>847</v>
+        <v>2095</v>
       </c>
       <c r="F48" s="4" t="n"/>
       <c r="G48" s="4" t="n"/>
       <c r="H48" s="8" t="n"/>
       <c r="I48" s="6" t="n"/>
-      <c r="J48" s="9" t="n"/>
+      <c r="J48" s="9" t="n">
+        <v>46302</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>상향1차</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>와이씨</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>232140</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>1861</v>
+        <v>545</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>2611</v>
+        <v>726</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>3176</v>
+        <v>847</v>
       </c>
       <c r="F49" s="4" t="n"/>
       <c r="G49" s="4" t="n"/>
@@ -1779,22 +1775,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>원익QNC</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>074600</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>1081</v>
+        <v>1861</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>1407</v>
+        <v>2611</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>1638</v>
+        <v>3176</v>
       </c>
       <c r="F50" s="4" t="n"/>
       <c r="G50" s="4" t="n"/>
@@ -1805,22 +1801,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>원익QNC</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>104830</t>
+          <t>074600</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>719</v>
+        <v>1081</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>922</v>
+        <v>1407</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>1040</v>
+        <v>1638</v>
       </c>
       <c r="F51" s="4" t="n"/>
       <c r="G51" s="4" t="n"/>
@@ -1831,22 +1827,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>유진테크</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>084370</t>
+          <t>104830</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>1027</v>
+        <v>719</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>1319</v>
+        <v>922</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>1390</v>
+        <v>1040</v>
       </c>
       <c r="F52" s="4" t="n"/>
       <c r="G52" s="4" t="n"/>
@@ -1857,22 +1853,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>이수페타시스</t>
+          <t>유진테크</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>007660</t>
+          <t>084370</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>3272</v>
+        <v>1027</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>4604</v>
+        <v>1319</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>5890</v>
+        <v>1390</v>
       </c>
       <c r="F53" s="4" t="n"/>
       <c r="G53" s="4" t="n"/>
@@ -1883,22 +1879,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>이수페타시스</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>102710</t>
+          <t>007660</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>823</v>
+        <v>3272</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>1181</v>
+        <v>4604</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>1670</v>
+        <v>5890</v>
       </c>
       <c r="F54" s="4" t="n"/>
       <c r="G54" s="4" t="n"/>
@@ -1909,22 +1905,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>039030</t>
+          <t>102710</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>1953</v>
+        <v>823</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>2540</v>
+        <v>1181</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>3193</v>
+        <v>1670</v>
       </c>
       <c r="F55" s="4" t="n"/>
       <c r="G55" s="4" t="n"/>
@@ -1935,21 +1931,23 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>제닉</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>123330</t>
+          <t>039030</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>296</v>
+        <v>1953</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>490</v>
-      </c>
-      <c r="E56" s="4" t="n"/>
+        <v>2540</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>3193</v>
+      </c>
       <c r="F56" s="4" t="n"/>
       <c r="G56" s="4" t="n"/>
       <c r="H56" s="8" t="n"/>
@@ -1959,23 +1957,21 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>제이엔티씨</t>
+          <t>제닉</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>123330</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>540</v>
+        <v>296</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>1637</v>
-      </c>
-      <c r="E57" s="4" t="n">
-        <v>1920</v>
-      </c>
+        <v>490</v>
+      </c>
+      <c r="E57" s="4" t="n"/>
       <c r="F57" s="4" t="n"/>
       <c r="G57" s="4" t="n"/>
       <c r="H57" s="8" t="n"/>
@@ -1985,22 +1981,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>제이엔티씨</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>204270</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>602</v>
+        <v>540</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>1535</v>
+        <v>1637</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>3165</v>
+        <v>1920</v>
       </c>
       <c r="F58" s="4" t="n"/>
       <c r="G58" s="4" t="n"/>
@@ -2011,22 +2007,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>케이씨텍</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>281820</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>1462</v>
+        <v>602</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>2011</v>
+        <v>1535</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>2170</v>
+        <v>3165</v>
       </c>
       <c r="F59" s="4" t="n"/>
       <c r="G59" s="4" t="n"/>
@@ -2037,19 +2033,23 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>케이엔제이</t>
+          <t>케이씨텍</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>272110</t>
+          <t>281820</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>320</v>
-      </c>
-      <c r="D60" s="4" t="n"/>
-      <c r="E60" s="4" t="n"/>
+        <v>1462</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>2170</v>
+      </c>
       <c r="F60" s="4" t="n"/>
       <c r="G60" s="4" t="n"/>
       <c r="H60" s="8" t="n"/>
@@ -2059,23 +2059,19 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>케이엔제이</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>007810</t>
+          <t>272110</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>1467</v>
-      </c>
-      <c r="D61" s="4" t="n">
-        <v>2229</v>
-      </c>
-      <c r="E61" s="4" t="n">
-        <v>2935</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="D61" s="4" t="n"/>
+      <c r="E61" s="4" t="n"/>
       <c r="F61" s="4" t="n"/>
       <c r="G61" s="4" t="n"/>
       <c r="H61" s="8" t="n"/>
@@ -2085,22 +2081,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>007810</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>1289</v>
+        <v>1467</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>1707</v>
+        <v>2229</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>2083</v>
+        <v>2935</v>
       </c>
       <c r="F62" s="4" t="n"/>
       <c r="G62" s="4" t="n"/>
@@ -2111,22 +2107,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>095610</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>1014</v>
+        <v>1289</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>1348</v>
+        <v>1707</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>1823</v>
+        <v>2083</v>
       </c>
       <c r="F63" s="4" t="n"/>
       <c r="G63" s="4" t="n"/>
@@ -2137,22 +2133,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>테크윙</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>089030</t>
+          <t>095610</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>985</v>
+        <v>1014</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>1729</v>
+        <v>1348</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>2310</v>
+        <v>1823</v>
       </c>
       <c r="F64" s="4" t="n"/>
       <c r="G64" s="4" t="n"/>
@@ -2163,22 +2159,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>티씨케이</t>
+          <t>테크윙</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>064760</t>
+          <t>089030</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>1258</v>
+        <v>985</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>1660</v>
+        <v>1729</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>2109</v>
+        <v>2310</v>
       </c>
       <c r="F65" s="4" t="n"/>
       <c r="G65" s="4" t="n"/>
@@ -2189,22 +2185,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>티씨케이</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>064760</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>1505</v>
+        <v>1258</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>1921</v>
+        <v>1660</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>2355</v>
+        <v>2109</v>
       </c>
       <c r="F66" s="4" t="n"/>
       <c r="G66" s="4" t="n"/>
@@ -2215,22 +2211,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>554</v>
+        <v>1505</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>799</v>
+        <v>1921</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>1278</v>
+        <v>2355</v>
       </c>
       <c r="F67" s="4" t="n"/>
       <c r="G67" s="4" t="n"/>
@@ -2241,79 +2237,79 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>440110</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>859</v>
+        <v>554</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>2158</v>
+        <v>799</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>2618</v>
+        <v>1278</v>
       </c>
       <c r="F68" s="4" t="n"/>
       <c r="G68" s="4" t="n"/>
       <c r="H68" s="8" t="n"/>
       <c r="I68" s="6" t="n"/>
       <c r="J68" s="9" t="n"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>8/5 상향</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>파라다이스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>034230</t>
+          <t>440110</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>1881</v>
+        <v>859</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>2277</v>
+        <v>2158</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>2479</v>
+        <v>2618</v>
       </c>
       <c r="F69" s="4" t="n"/>
       <c r="G69" s="4" t="n"/>
       <c r="H69" s="8" t="n"/>
       <c r="I69" s="6" t="n"/>
       <c r="J69" s="9" t="n"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>8/5 상향</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>파라다이스</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>034230</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>2655</v>
+        <v>1881</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>3278</v>
+        <v>2277</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>3920</v>
+        <v>2479</v>
       </c>
       <c r="F70" s="4" t="n"/>
       <c r="G70" s="4" t="n"/>
@@ -2324,22 +2320,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>624</v>
+        <v>2655</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>733</v>
+        <v>3278</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>750</v>
+        <v>3920</v>
       </c>
       <c r="F71" s="4" t="n"/>
       <c r="G71" s="4" t="n"/>
@@ -2350,78 +2346,76 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>319660</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>1897</v>
+        <v>624</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>2325</v>
+        <v>733</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>2393</v>
+        <v>750</v>
       </c>
       <c r="F72" s="4" t="n"/>
       <c r="G72" s="4" t="n"/>
       <c r="H72" s="8" t="n"/>
       <c r="I72" s="6" t="n"/>
-      <c r="J72" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
+      <c r="J72" s="9" t="n"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>067310</t>
+          <t>319660</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>3154</v>
+        <v>1897</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>3785</v>
+        <v>2325</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>4361</v>
+        <v>2393</v>
       </c>
       <c r="F73" s="4" t="n"/>
       <c r="G73" s="4" t="n"/>
       <c r="H73" s="8" t="n"/>
       <c r="I73" s="6" t="n"/>
-      <c r="J73" s="9" t="n"/>
+      <c r="J73" s="9" t="n">
+        <v>46302</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>166090</t>
+          <t>067310</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>1002</v>
+        <v>3154</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>1335</v>
+        <v>3785</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>1450</v>
+        <v>4361</v>
       </c>
       <c r="F74" s="4" t="n"/>
       <c r="G74" s="4" t="n"/>
@@ -2432,22 +2426,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>하이록코리아</t>
+          <t>하나머티리얼즈</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>013030</t>
+          <t>166090</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>608</v>
+        <v>1002</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>714</v>
+        <v>1335</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>726</v>
+        <v>1450</v>
       </c>
       <c r="F75" s="4" t="n"/>
       <c r="G75" s="4" t="n"/>
@@ -2458,22 +2452,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>하이록코리아</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>352820</t>
+          <t>013030</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>2860</v>
+        <v>608</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>4871</v>
+        <v>714</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>5432</v>
+        <v>726</v>
       </c>
       <c r="F76" s="4" t="n"/>
       <c r="G76" s="4" t="n"/>
@@ -2484,22 +2478,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>한국카본</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>017960</t>
+          <t>352820</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>1798</v>
+        <v>2860</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>1964</v>
+        <v>4871</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>1947</v>
+        <v>5432</v>
       </c>
       <c r="F77" s="4" t="n"/>
       <c r="G77" s="4" t="n"/>
@@ -2510,22 +2504,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>한국항공우주</t>
+          <t>한국카본</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>047810</t>
+          <t>017960</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>4736</v>
+        <v>1798</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>6744</v>
+        <v>1964</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>8136</v>
+        <v>1947</v>
       </c>
       <c r="F78" s="4" t="n"/>
       <c r="G78" s="4" t="n"/>
@@ -2536,22 +2530,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>한솔케미칼</t>
+          <t>한국항공우주</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>014680</t>
+          <t>047810</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>1889</v>
+        <v>4736</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>2374</v>
+        <v>6744</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>2983</v>
+        <v>8136</v>
       </c>
       <c r="F79" s="4" t="n"/>
       <c r="G79" s="4" t="n"/>
@@ -2562,17 +2556,23 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>한솔케미칼</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>078350</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="n"/>
-      <c r="D80" s="4" t="n"/>
-      <c r="E80" s="4" t="n"/>
+          <t>014680</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>1889</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>2374</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>2983</v>
+      </c>
       <c r="F80" s="4" t="n"/>
       <c r="G80" s="4" t="n"/>
       <c r="H80" s="8" t="n"/>
@@ -2582,86 +2582,98 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>082740</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>2442</v>
-      </c>
-      <c r="D81" t="n">
-        <v>3679</v>
-      </c>
-      <c r="E81" t="n">
-        <v>4513</v>
+          <t>078350</t>
+        </is>
       </c>
       <c r="J81" s="10" t="n"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>해성디에스</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>195870</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>897</v>
+        <v>2442</v>
       </c>
       <c r="D82" t="n">
-        <v>1283</v>
+        <v>3679</v>
       </c>
       <c r="E82" t="n">
-        <v>1547</v>
+        <v>4513</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>현대이지웰</t>
+          <t>해성디에스</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>090850</t>
+          <t>195870</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>260</v>
+        <v>897</v>
       </c>
       <c r="D83" t="n">
-        <v>280</v>
+        <v>1283</v>
       </c>
       <c r="E83" t="n">
-        <v>300</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>현대이지웰</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>420770</t>
+          <t>090850</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>344</v>
+        <v>260</v>
       </c>
       <c r="D84" t="n">
-        <v>955</v>
+        <v>280</v>
       </c>
       <c r="E84" t="n">
-        <v>840</v>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>091580</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>260</v>
+      </c>
+      <c r="D85" t="n">
+        <v>331</v>
+      </c>
+      <c r="E85" t="n">
+        <v>440</v>
       </c>
     </row>
   </sheetData>

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:K86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1418,22 +1418,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>319</v>
+        <v>260</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>427</v>
+        <v>331</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>486</v>
+        <v>440</v>
       </c>
       <c r="F37" s="4" t="n"/>
       <c r="G37" s="4" t="n"/>
@@ -1444,22 +1444,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>세진중공업</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>075580</t>
+          <t>252990</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>861</v>
+        <v>319</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>1010</v>
+        <v>427</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>1056</v>
+        <v>486</v>
       </c>
       <c r="F38" s="4" t="n"/>
       <c r="G38" s="4" t="n"/>
@@ -1470,22 +1470,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>솔브레인</t>
+          <t>세진중공업</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>357780</t>
+          <t>075580</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>1941</v>
+        <v>861</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>2518</v>
+        <v>1010</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>3133</v>
+        <v>1056</v>
       </c>
       <c r="F39" s="4" t="n"/>
       <c r="G39" s="4" t="n"/>
@@ -1496,22 +1496,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>솔브레인</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>357780</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>2750</v>
+        <v>1941</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>3532</v>
+        <v>2518</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>4124</v>
+        <v>3133</v>
       </c>
       <c r="F40" s="4" t="n"/>
       <c r="G40" s="4" t="n"/>
@@ -1522,79 +1522,85 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>2583</v>
+        <v>2750</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>4385</v>
+        <v>3532</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>5658</v>
+        <v>4124</v>
       </c>
       <c r="F41" s="4" t="n"/>
       <c r="G41" s="4" t="n"/>
-      <c r="H41" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>회사/증권사 컨센서스</t>
-        </is>
-      </c>
-      <c r="J41" s="9" t="n">
-        <v>46302</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>예시값 - 실제 컨센서스로 수정</t>
-        </is>
-      </c>
+      <c r="H41" s="8" t="n"/>
+      <c r="I41" s="6" t="n"/>
+      <c r="J41" s="9" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>싸이맥스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>160980</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>260</v>
+        <v>2583</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>450</v>
-      </c>
-      <c r="E42" s="4" t="n"/>
+        <v>4385</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>5658</v>
+      </c>
       <c r="F42" s="4" t="n"/>
       <c r="G42" s="4" t="n"/>
-      <c r="H42" s="8" t="n"/>
-      <c r="I42" s="6" t="n"/>
-      <c r="J42" s="9" t="n"/>
+      <c r="H42" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>회사/증권사 컨센서스</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>46302</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>예시값 - 실제 컨센서스로 수정</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>에스앤에스텍</t>
+          <t>싸이맥스</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>101490</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="4" t="n"/>
+          <t>160980</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>260</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>450</v>
+      </c>
       <c r="E43" s="4" t="n"/>
       <c r="F43" s="4" t="n"/>
       <c r="G43" s="4" t="n"/>
@@ -1605,23 +1611,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>에스티아이</t>
+          <t>에스앤에스텍</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>039440</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>751</v>
-      </c>
-      <c r="D44" s="4" t="n">
-        <v>1306</v>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>1341</v>
-      </c>
+          <t>101490</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
       <c r="F44" s="4" t="n"/>
       <c r="G44" s="4" t="n"/>
       <c r="H44" s="8" t="n"/>
@@ -1631,21 +1631,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>에스티아이</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>039440</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>231</v>
+        <v>751</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>371</v>
-      </c>
-      <c r="E45" s="4" t="n"/>
+        <v>1306</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>1341</v>
+      </c>
       <c r="F45" s="4" t="n"/>
       <c r="G45" s="4" t="n"/>
       <c r="H45" s="8" t="n"/>
@@ -1655,19 +1657,19 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>엑시콘</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>092870</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>148</v>
+        <v>231</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>282</v>
+        <v>371</v>
       </c>
       <c r="E46" s="4" t="n"/>
       <c r="F46" s="4" t="n"/>
@@ -1679,118 +1681,116 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>엑시콘</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>092870</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>734</v>
+        <v>148</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>1174</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>1545</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="E47" s="4" t="n"/>
       <c r="F47" s="4" t="n"/>
       <c r="G47" s="4" t="n"/>
       <c r="H47" s="8" t="n"/>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">컨센서스 </t>
-        </is>
-      </c>
-      <c r="J47" s="9" t="n">
-        <v>46254</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>상향 650&gt;734(1회)</t>
-        </is>
-      </c>
+      <c r="I47" s="6" t="n"/>
+      <c r="J47" s="9" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>033160</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>1139</v>
+        <v>734</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>1744</v>
+        <v>1174</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>2095</v>
+        <v>1545</v>
       </c>
       <c r="F48" s="4" t="n"/>
       <c r="G48" s="4" t="n"/>
       <c r="H48" s="8" t="n"/>
-      <c r="I48" s="6" t="n"/>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">컨센서스 </t>
+        </is>
+      </c>
       <c r="J48" s="9" t="n">
-        <v>46302</v>
+        <v>46254</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>상향1차</t>
+          <t>상향 650&gt;734(1회)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>와이씨</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>232140</t>
+          <t>033160</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>545</v>
+        <v>1139</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>726</v>
+        <v>1744</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>847</v>
+        <v>2095</v>
       </c>
       <c r="F49" s="4" t="n"/>
       <c r="G49" s="4" t="n"/>
       <c r="H49" s="8" t="n"/>
       <c r="I49" s="6" t="n"/>
-      <c r="J49" s="9" t="n"/>
+      <c r="J49" s="9" t="n">
+        <v>46302</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>상향1차</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>와이씨</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>232140</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>1861</v>
+        <v>545</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>2611</v>
+        <v>726</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>3176</v>
+        <v>847</v>
       </c>
       <c r="F50" s="4" t="n"/>
       <c r="G50" s="4" t="n"/>
@@ -1801,22 +1801,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>원익QNC</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>074600</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>1081</v>
+        <v>1861</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>1407</v>
+        <v>2611</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>1638</v>
+        <v>3176</v>
       </c>
       <c r="F51" s="4" t="n"/>
       <c r="G51" s="4" t="n"/>
@@ -1827,22 +1827,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>원익QNC</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>104830</t>
+          <t>074600</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>719</v>
+        <v>1081</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>922</v>
+        <v>1407</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>1040</v>
+        <v>1638</v>
       </c>
       <c r="F52" s="4" t="n"/>
       <c r="G52" s="4" t="n"/>
@@ -1853,22 +1853,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>유진테크</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>084370</t>
+          <t>104830</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>1027</v>
+        <v>719</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>1319</v>
+        <v>922</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>1390</v>
+        <v>1040</v>
       </c>
       <c r="F53" s="4" t="n"/>
       <c r="G53" s="4" t="n"/>
@@ -1879,22 +1879,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>이수페타시스</t>
+          <t>유진테크</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>007660</t>
+          <t>084370</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>3272</v>
+        <v>1027</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>4604</v>
+        <v>1319</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>5890</v>
+        <v>1390</v>
       </c>
       <c r="F54" s="4" t="n"/>
       <c r="G54" s="4" t="n"/>
@@ -1905,22 +1905,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>이수페타시스</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>102710</t>
+          <t>007660</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>823</v>
+        <v>3272</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>1181</v>
+        <v>4604</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>1670</v>
+        <v>5890</v>
       </c>
       <c r="F55" s="4" t="n"/>
       <c r="G55" s="4" t="n"/>
@@ -1931,22 +1931,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>039030</t>
+          <t>102710</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>1953</v>
+        <v>823</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>2540</v>
+        <v>1181</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>3193</v>
+        <v>1670</v>
       </c>
       <c r="F56" s="4" t="n"/>
       <c r="G56" s="4" t="n"/>
@@ -1957,21 +1957,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>제닉</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>123330</t>
+          <t>039030</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>296</v>
+        <v>1953</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>490</v>
-      </c>
-      <c r="E57" s="4" t="n"/>
+        <v>2540</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>3193</v>
+      </c>
       <c r="F57" s="4" t="n"/>
       <c r="G57" s="4" t="n"/>
       <c r="H57" s="8" t="n"/>
@@ -1981,23 +1983,21 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>제이엔티씨</t>
+          <t>제닉</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>123330</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>540</v>
+        <v>296</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>1637</v>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>1920</v>
-      </c>
+        <v>490</v>
+      </c>
+      <c r="E58" s="4" t="n"/>
       <c r="F58" s="4" t="n"/>
       <c r="G58" s="4" t="n"/>
       <c r="H58" s="8" t="n"/>
@@ -2007,22 +2007,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>제이엔티씨</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>204270</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>602</v>
+        <v>540</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>1535</v>
+        <v>1637</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>3165</v>
+        <v>1920</v>
       </c>
       <c r="F59" s="4" t="n"/>
       <c r="G59" s="4" t="n"/>
@@ -2033,22 +2033,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>케이씨텍</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>281820</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1462</v>
+        <v>602</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>2011</v>
+        <v>1535</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>2170</v>
+        <v>3165</v>
       </c>
       <c r="F60" s="4" t="n"/>
       <c r="G60" s="4" t="n"/>
@@ -2059,19 +2059,23 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>케이엔제이</t>
+          <t>케이씨텍</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>272110</t>
+          <t>281820</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>320</v>
-      </c>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
+        <v>1462</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>2170</v>
+      </c>
       <c r="F61" s="4" t="n"/>
       <c r="G61" s="4" t="n"/>
       <c r="H61" s="8" t="n"/>
@@ -2081,23 +2085,19 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>케이엔제이</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>007810</t>
+          <t>272110</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>1467</v>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>2229</v>
-      </c>
-      <c r="E62" s="4" t="n">
-        <v>2935</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="D62" s="4" t="n"/>
+      <c r="E62" s="4" t="n"/>
       <c r="F62" s="4" t="n"/>
       <c r="G62" s="4" t="n"/>
       <c r="H62" s="8" t="n"/>
@@ -2107,22 +2107,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>007810</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>1289</v>
+        <v>1467</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>1707</v>
+        <v>2229</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>2083</v>
+        <v>2935</v>
       </c>
       <c r="F63" s="4" t="n"/>
       <c r="G63" s="4" t="n"/>
@@ -2133,22 +2133,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>095610</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>1014</v>
+        <v>1289</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>1348</v>
+        <v>1707</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>1823</v>
+        <v>2083</v>
       </c>
       <c r="F64" s="4" t="n"/>
       <c r="G64" s="4" t="n"/>
@@ -2159,22 +2159,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>테크윙</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>089030</t>
+          <t>095610</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>985</v>
+        <v>1014</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>1729</v>
+        <v>1348</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>2310</v>
+        <v>1823</v>
       </c>
       <c r="F65" s="4" t="n"/>
       <c r="G65" s="4" t="n"/>
@@ -2185,22 +2185,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>티씨케이</t>
+          <t>테크윙</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>064760</t>
+          <t>089030</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>1258</v>
+        <v>985</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>1660</v>
+        <v>1729</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>2109</v>
+        <v>2310</v>
       </c>
       <c r="F66" s="4" t="n"/>
       <c r="G66" s="4" t="n"/>
@@ -2211,22 +2211,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>티씨케이</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>064760</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>1505</v>
+        <v>1258</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>1921</v>
+        <v>1660</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>2355</v>
+        <v>2109</v>
       </c>
       <c r="F67" s="4" t="n"/>
       <c r="G67" s="4" t="n"/>
@@ -2237,22 +2237,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>554</v>
+        <v>1505</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>799</v>
+        <v>1921</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>1278</v>
+        <v>2355</v>
       </c>
       <c r="F68" s="4" t="n"/>
       <c r="G68" s="4" t="n"/>
@@ -2263,79 +2263,79 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>440110</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>859</v>
+        <v>554</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>2158</v>
+        <v>799</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>2618</v>
+        <v>1278</v>
       </c>
       <c r="F69" s="4" t="n"/>
       <c r="G69" s="4" t="n"/>
       <c r="H69" s="8" t="n"/>
       <c r="I69" s="6" t="n"/>
       <c r="J69" s="9" t="n"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>8/5 상향</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>파라다이스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>034230</t>
+          <t>440110</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>1881</v>
+        <v>859</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>2277</v>
+        <v>2158</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>2479</v>
+        <v>2618</v>
       </c>
       <c r="F70" s="4" t="n"/>
       <c r="G70" s="4" t="n"/>
       <c r="H70" s="8" t="n"/>
       <c r="I70" s="6" t="n"/>
       <c r="J70" s="9" t="n"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>8/5 상향</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>파라다이스</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>034230</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>2655</v>
+        <v>1881</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>3278</v>
+        <v>2277</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>3920</v>
+        <v>2479</v>
       </c>
       <c r="F71" s="4" t="n"/>
       <c r="G71" s="4" t="n"/>
@@ -2346,22 +2346,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>624</v>
+        <v>2655</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>733</v>
+        <v>3278</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>750</v>
+        <v>3920</v>
       </c>
       <c r="F72" s="4" t="n"/>
       <c r="G72" s="4" t="n"/>
@@ -2372,76 +2372,76 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>319660</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>1897</v>
+        <v>624</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>2325</v>
+        <v>733</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>2393</v>
+        <v>750</v>
       </c>
       <c r="F73" s="4" t="n"/>
       <c r="G73" s="4" t="n"/>
       <c r="H73" s="8" t="n"/>
       <c r="I73" s="6" t="n"/>
-      <c r="J73" s="9" t="n">
-        <v>46302</v>
-      </c>
+      <c r="J73" s="9" t="n"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>067310</t>
+          <t>319660</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>3154</v>
+        <v>1897</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>3785</v>
+        <v>2325</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>4361</v>
+        <v>2393</v>
       </c>
       <c r="F74" s="4" t="n"/>
       <c r="G74" s="4" t="n"/>
       <c r="H74" s="8" t="n"/>
       <c r="I74" s="6" t="n"/>
-      <c r="J74" s="9" t="n"/>
+      <c r="J74" s="9" t="n">
+        <v>46302</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>166090</t>
+          <t>067310</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>1002</v>
+        <v>3154</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>1335</v>
+        <v>3785</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>1450</v>
+        <v>4361</v>
       </c>
       <c r="F75" s="4" t="n"/>
       <c r="G75" s="4" t="n"/>
@@ -2452,22 +2452,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>하이록코리아</t>
+          <t>하나머티리얼즈</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>013030</t>
+          <t>166090</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>608</v>
+        <v>1002</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>714</v>
+        <v>1335</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>726</v>
+        <v>1450</v>
       </c>
       <c r="F76" s="4" t="n"/>
       <c r="G76" s="4" t="n"/>
@@ -2478,22 +2478,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>하이록코리아</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>352820</t>
+          <t>013030</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>2860</v>
+        <v>608</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>4871</v>
+        <v>714</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>5432</v>
+        <v>726</v>
       </c>
       <c r="F77" s="4" t="n"/>
       <c r="G77" s="4" t="n"/>
@@ -2504,22 +2504,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>한국카본</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>017960</t>
+          <t>352820</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>1798</v>
+        <v>2860</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>1964</v>
+        <v>4871</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>1947</v>
+        <v>5432</v>
       </c>
       <c r="F78" s="4" t="n"/>
       <c r="G78" s="4" t="n"/>
@@ -2530,22 +2530,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>한국항공우주</t>
+          <t>한국카본</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>047810</t>
+          <t>017960</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>4736</v>
+        <v>1798</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>6744</v>
+        <v>1964</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>8136</v>
+        <v>1947</v>
       </c>
       <c r="F79" s="4" t="n"/>
       <c r="G79" s="4" t="n"/>
@@ -2556,22 +2556,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>한솔케미칼</t>
+          <t>한국항공우주</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>014680</t>
+          <t>047810</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>1889</v>
+        <v>4736</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>2374</v>
+        <v>6744</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>2983</v>
+        <v>8136</v>
       </c>
       <c r="F80" s="4" t="n"/>
       <c r="G80" s="4" t="n"/>
@@ -2582,98 +2582,119 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>한솔케미칼</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>078350</t>
-        </is>
+          <t>014680</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1889</v>
+      </c>
+      <c r="D81" t="n">
+        <v>2374</v>
+      </c>
+      <c r="E81" t="n">
+        <v>2983</v>
       </c>
       <c r="J81" s="10" t="n"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>082740</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>2442</v>
-      </c>
-      <c r="D82" t="n">
-        <v>3679</v>
-      </c>
-      <c r="E82" t="n">
-        <v>4513</v>
+          <t>078350</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>해성디에스</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>195870</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>897</v>
+        <v>2442</v>
       </c>
       <c r="D83" t="n">
-        <v>1283</v>
+        <v>3679</v>
       </c>
       <c r="E83" t="n">
-        <v>1547</v>
+        <v>4513</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>현대이지웰</t>
+          <t>해성디에스</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>090850</t>
+          <t>195870</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>260</v>
+        <v>897</v>
       </c>
       <c r="D84" t="n">
-        <v>280</v>
+        <v>1283</v>
       </c>
       <c r="E84" t="n">
-        <v>300</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>현대이지웰</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>090850</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>260</v>
       </c>
       <c r="D85" t="n">
-        <v>331</v>
+        <v>280</v>
       </c>
       <c r="E85" t="n">
-        <v>440</v>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>178320</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>635</v>
+      </c>
+      <c r="D86" t="n">
+        <v>2904</v>
+      </c>
+      <c r="E86" t="n">
+        <v>3492</v>
       </c>
     </row>
   </sheetData>

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K86"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1470,22 +1470,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>세진중공업</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>075580</t>
+          <t>178320</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>861</v>
+        <v>635</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>1010</v>
+        <v>2904</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>1056</v>
+        <v>3492</v>
       </c>
       <c r="F39" s="4" t="n"/>
       <c r="G39" s="4" t="n"/>
@@ -1496,22 +1496,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>솔브레인</t>
+          <t>세진중공업</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>357780</t>
+          <t>075580</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>1941</v>
+        <v>861</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>2518</v>
+        <v>1010</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>3133</v>
+        <v>1056</v>
       </c>
       <c r="F40" s="4" t="n"/>
       <c r="G40" s="4" t="n"/>
@@ -1522,22 +1522,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>솔브레인</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>357780</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>2750</v>
+        <v>1941</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>3532</v>
+        <v>2518</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>4124</v>
+        <v>3133</v>
       </c>
       <c r="F41" s="4" t="n"/>
       <c r="G41" s="4" t="n"/>
@@ -1548,79 +1548,85 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>2583</v>
+        <v>2750</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>4385</v>
+        <v>3532</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>5658</v>
+        <v>4124</v>
       </c>
       <c r="F42" s="4" t="n"/>
       <c r="G42" s="4" t="n"/>
-      <c r="H42" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>회사/증권사 컨센서스</t>
-        </is>
-      </c>
-      <c r="J42" s="9" t="n">
-        <v>46302</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>예시값 - 실제 컨센서스로 수정</t>
-        </is>
-      </c>
+      <c r="H42" s="8" t="n"/>
+      <c r="I42" s="6" t="n"/>
+      <c r="J42" s="9" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>싸이맥스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>160980</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>260</v>
+        <v>2583</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>450</v>
-      </c>
-      <c r="E43" s="4" t="n"/>
+        <v>4385</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>5658</v>
+      </c>
       <c r="F43" s="4" t="n"/>
       <c r="G43" s="4" t="n"/>
-      <c r="H43" s="8" t="n"/>
-      <c r="I43" s="6" t="n"/>
-      <c r="J43" s="9" t="n"/>
+      <c r="H43" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>회사/증권사 컨센서스</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>46302</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>예시값 - 실제 컨센서스로 수정</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>에스앤에스텍</t>
+          <t>싸이맥스</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>101490</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="n"/>
+          <t>160980</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>260</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>450</v>
+      </c>
       <c r="E44" s="4" t="n"/>
       <c r="F44" s="4" t="n"/>
       <c r="G44" s="4" t="n"/>
@@ -1631,23 +1637,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>에스티아이</t>
+          <t>에스앤에스텍</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>039440</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>751</v>
-      </c>
-      <c r="D45" s="4" t="n">
-        <v>1306</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>1341</v>
-      </c>
+          <t>101490</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
       <c r="F45" s="4" t="n"/>
       <c r="G45" s="4" t="n"/>
       <c r="H45" s="8" t="n"/>
@@ -1657,21 +1657,23 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>에스티아이</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>039440</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>231</v>
+        <v>751</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>371</v>
-      </c>
-      <c r="E46" s="4" t="n"/>
+        <v>1306</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>1341</v>
+      </c>
       <c r="F46" s="4" t="n"/>
       <c r="G46" s="4" t="n"/>
       <c r="H46" s="8" t="n"/>
@@ -1681,19 +1683,19 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>엑시콘</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>092870</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>148</v>
+        <v>231</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>282</v>
+        <v>371</v>
       </c>
       <c r="E47" s="4" t="n"/>
       <c r="F47" s="4" t="n"/>
@@ -1705,118 +1707,116 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>엑시콘</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>092870</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>734</v>
+        <v>148</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>1174</v>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>1545</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="E48" s="4" t="n"/>
       <c r="F48" s="4" t="n"/>
       <c r="G48" s="4" t="n"/>
       <c r="H48" s="8" t="n"/>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">컨센서스 </t>
-        </is>
-      </c>
-      <c r="J48" s="9" t="n">
-        <v>46254</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>상향 650&gt;734(1회)</t>
-        </is>
-      </c>
+      <c r="I48" s="6" t="n"/>
+      <c r="J48" s="9" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>033160</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>1139</v>
+        <v>734</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>1744</v>
+        <v>1174</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>2095</v>
+        <v>1545</v>
       </c>
       <c r="F49" s="4" t="n"/>
       <c r="G49" s="4" t="n"/>
       <c r="H49" s="8" t="n"/>
-      <c r="I49" s="6" t="n"/>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">컨센서스 </t>
+        </is>
+      </c>
       <c r="J49" s="9" t="n">
-        <v>46302</v>
+        <v>46254</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>상향1차</t>
+          <t>상향 650&gt;734(1회)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>와이씨</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>232140</t>
+          <t>033160</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>545</v>
+        <v>1139</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>726</v>
+        <v>1744</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>847</v>
+        <v>2095</v>
       </c>
       <c r="F50" s="4" t="n"/>
       <c r="G50" s="4" t="n"/>
       <c r="H50" s="8" t="n"/>
       <c r="I50" s="6" t="n"/>
-      <c r="J50" s="9" t="n"/>
+      <c r="J50" s="9" t="n">
+        <v>46302</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>상향1차</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>와이씨</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>232140</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>1861</v>
+        <v>545</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>2611</v>
+        <v>726</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>3176</v>
+        <v>847</v>
       </c>
       <c r="F51" s="4" t="n"/>
       <c r="G51" s="4" t="n"/>
@@ -1827,22 +1827,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>원익QNC</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>074600</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>1081</v>
+        <v>1861</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>1407</v>
+        <v>2611</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>1638</v>
+        <v>3176</v>
       </c>
       <c r="F52" s="4" t="n"/>
       <c r="G52" s="4" t="n"/>
@@ -1853,22 +1853,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>원익QNC</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>104830</t>
+          <t>074600</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>719</v>
+        <v>1081</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>922</v>
+        <v>1407</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>1040</v>
+        <v>1638</v>
       </c>
       <c r="F53" s="4" t="n"/>
       <c r="G53" s="4" t="n"/>
@@ -1879,22 +1879,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>유진테크</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>084370</t>
+          <t>104830</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>1027</v>
+        <v>719</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>1319</v>
+        <v>922</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>1390</v>
+        <v>1040</v>
       </c>
       <c r="F54" s="4" t="n"/>
       <c r="G54" s="4" t="n"/>
@@ -1905,22 +1905,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>이수페타시스</t>
+          <t>유진테크</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>007660</t>
+          <t>084370</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>3272</v>
+        <v>1027</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>4604</v>
+        <v>1319</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>5890</v>
+        <v>1390</v>
       </c>
       <c r="F55" s="4" t="n"/>
       <c r="G55" s="4" t="n"/>
@@ -1931,22 +1931,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>이수페타시스</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>102710</t>
+          <t>007660</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>823</v>
+        <v>3272</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>1181</v>
+        <v>4604</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>1670</v>
+        <v>5890</v>
       </c>
       <c r="F56" s="4" t="n"/>
       <c r="G56" s="4" t="n"/>
@@ -1957,22 +1957,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>039030</t>
+          <t>102710</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>1953</v>
+        <v>823</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>2540</v>
+        <v>1181</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>3193</v>
+        <v>1670</v>
       </c>
       <c r="F57" s="4" t="n"/>
       <c r="G57" s="4" t="n"/>
@@ -1983,21 +1983,23 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>제닉</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>123330</t>
+          <t>039030</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>296</v>
+        <v>1953</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>490</v>
-      </c>
-      <c r="E58" s="4" t="n"/>
+        <v>2540</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>3193</v>
+      </c>
       <c r="F58" s="4" t="n"/>
       <c r="G58" s="4" t="n"/>
       <c r="H58" s="8" t="n"/>
@@ -2007,23 +2009,21 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>제이엔티씨</t>
+          <t>제닉</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>123330</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>540</v>
+        <v>296</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>1637</v>
-      </c>
-      <c r="E59" s="4" t="n">
-        <v>1920</v>
-      </c>
+        <v>490</v>
+      </c>
+      <c r="E59" s="4" t="n"/>
       <c r="F59" s="4" t="n"/>
       <c r="G59" s="4" t="n"/>
       <c r="H59" s="8" t="n"/>
@@ -2033,22 +2033,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>제이엔티씨</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>204270</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>602</v>
+        <v>540</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>1535</v>
+        <v>1637</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>3165</v>
+        <v>1920</v>
       </c>
       <c r="F60" s="4" t="n"/>
       <c r="G60" s="4" t="n"/>
@@ -2059,22 +2059,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>케이씨텍</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>281820</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>1462</v>
+        <v>602</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>2011</v>
+        <v>1535</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>2170</v>
+        <v>3165</v>
       </c>
       <c r="F61" s="4" t="n"/>
       <c r="G61" s="4" t="n"/>
@@ -2085,19 +2085,23 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>케이엔제이</t>
+          <t>케이씨텍</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>272110</t>
+          <t>281820</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>320</v>
-      </c>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
+        <v>1462</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>2170</v>
+      </c>
       <c r="F62" s="4" t="n"/>
       <c r="G62" s="4" t="n"/>
       <c r="H62" s="8" t="n"/>
@@ -2107,23 +2111,19 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>케이엔제이</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>007810</t>
+          <t>272110</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>1467</v>
-      </c>
-      <c r="D63" s="4" t="n">
-        <v>2229</v>
-      </c>
-      <c r="E63" s="4" t="n">
-        <v>2935</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="D63" s="4" t="n"/>
+      <c r="E63" s="4" t="n"/>
       <c r="F63" s="4" t="n"/>
       <c r="G63" s="4" t="n"/>
       <c r="H63" s="8" t="n"/>
@@ -2133,22 +2133,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>007810</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>1289</v>
+        <v>1467</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>1707</v>
+        <v>2229</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>2083</v>
+        <v>2935</v>
       </c>
       <c r="F64" s="4" t="n"/>
       <c r="G64" s="4" t="n"/>
@@ -2159,22 +2159,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>095610</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>1014</v>
+        <v>1289</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>1348</v>
+        <v>1707</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>1823</v>
+        <v>2083</v>
       </c>
       <c r="F65" s="4" t="n"/>
       <c r="G65" s="4" t="n"/>
@@ -2185,22 +2185,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>테크윙</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>089030</t>
+          <t>095610</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>985</v>
+        <v>1014</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>1729</v>
+        <v>1348</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>2310</v>
+        <v>1823</v>
       </c>
       <c r="F66" s="4" t="n"/>
       <c r="G66" s="4" t="n"/>
@@ -2211,22 +2211,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>티씨케이</t>
+          <t>테크윙</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>064760</t>
+          <t>089030</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>1258</v>
+        <v>985</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>1660</v>
+        <v>1729</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>2109</v>
+        <v>2310</v>
       </c>
       <c r="F67" s="4" t="n"/>
       <c r="G67" s="4" t="n"/>
@@ -2237,22 +2237,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>티씨케이</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>064760</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>1505</v>
+        <v>1258</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>1921</v>
+        <v>1660</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>2355</v>
+        <v>2109</v>
       </c>
       <c r="F68" s="4" t="n"/>
       <c r="G68" s="4" t="n"/>
@@ -2263,22 +2263,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>554</v>
+        <v>1505</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>799</v>
+        <v>1921</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>1278</v>
+        <v>2355</v>
       </c>
       <c r="F69" s="4" t="n"/>
       <c r="G69" s="4" t="n"/>
@@ -2289,79 +2289,79 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>440110</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>859</v>
+        <v>554</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>2158</v>
+        <v>799</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>2618</v>
+        <v>1278</v>
       </c>
       <c r="F70" s="4" t="n"/>
       <c r="G70" s="4" t="n"/>
       <c r="H70" s="8" t="n"/>
       <c r="I70" s="6" t="n"/>
       <c r="J70" s="9" t="n"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>8/5 상향</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>파라다이스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>034230</t>
+          <t>440110</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>1881</v>
+        <v>859</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>2277</v>
+        <v>2158</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>2479</v>
+        <v>2618</v>
       </c>
       <c r="F71" s="4" t="n"/>
       <c r="G71" s="4" t="n"/>
       <c r="H71" s="8" t="n"/>
       <c r="I71" s="6" t="n"/>
       <c r="J71" s="9" t="n"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>8/5 상향</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>파라다이스</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>034230</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>2655</v>
+        <v>1881</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>3278</v>
+        <v>2277</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>3920</v>
+        <v>2479</v>
       </c>
       <c r="F72" s="4" t="n"/>
       <c r="G72" s="4" t="n"/>
@@ -2372,22 +2372,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>624</v>
+        <v>2655</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>733</v>
+        <v>3278</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>750</v>
+        <v>3920</v>
       </c>
       <c r="F73" s="4" t="n"/>
       <c r="G73" s="4" t="n"/>
@@ -2398,76 +2398,76 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>319660</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>1897</v>
+        <v>624</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>2325</v>
+        <v>733</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>2393</v>
+        <v>750</v>
       </c>
       <c r="F74" s="4" t="n"/>
       <c r="G74" s="4" t="n"/>
       <c r="H74" s="8" t="n"/>
       <c r="I74" s="6" t="n"/>
-      <c r="J74" s="9" t="n">
-        <v>46302</v>
-      </c>
+      <c r="J74" s="9" t="n"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>067310</t>
+          <t>319660</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>3154</v>
+        <v>1897</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>3785</v>
+        <v>2325</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>4361</v>
+        <v>2393</v>
       </c>
       <c r="F75" s="4" t="n"/>
       <c r="G75" s="4" t="n"/>
       <c r="H75" s="8" t="n"/>
       <c r="I75" s="6" t="n"/>
-      <c r="J75" s="9" t="n"/>
+      <c r="J75" s="9" t="n">
+        <v>46302</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>166090</t>
+          <t>067310</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>1002</v>
+        <v>3154</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>1335</v>
+        <v>3785</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>1450</v>
+        <v>4361</v>
       </c>
       <c r="F76" s="4" t="n"/>
       <c r="G76" s="4" t="n"/>
@@ -2478,22 +2478,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>하이록코리아</t>
+          <t>하나머티리얼즈</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>013030</t>
+          <t>166090</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>608</v>
+        <v>1002</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>714</v>
+        <v>1335</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>726</v>
+        <v>1450</v>
       </c>
       <c r="F77" s="4" t="n"/>
       <c r="G77" s="4" t="n"/>
@@ -2504,22 +2504,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>하이록코리아</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>352820</t>
+          <t>013030</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>2860</v>
+        <v>608</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>4871</v>
+        <v>714</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>5432</v>
+        <v>726</v>
       </c>
       <c r="F78" s="4" t="n"/>
       <c r="G78" s="4" t="n"/>
@@ -2530,22 +2530,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>한국카본</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>017960</t>
+          <t>352820</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>1798</v>
+        <v>2860</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>1964</v>
+        <v>4871</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>1947</v>
+        <v>5432</v>
       </c>
       <c r="F79" s="4" t="n"/>
       <c r="G79" s="4" t="n"/>
@@ -2556,22 +2556,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>한국항공우주</t>
+          <t>한국카본</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>047810</t>
+          <t>017960</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>4736</v>
+        <v>1798</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>6744</v>
+        <v>1964</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>8136</v>
+        <v>1947</v>
       </c>
       <c r="F80" s="4" t="n"/>
       <c r="G80" s="4" t="n"/>
@@ -2582,119 +2582,140 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>한솔케미칼</t>
+          <t>한국항공우주</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>014680</t>
+          <t>047810</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1889</v>
+        <v>4736</v>
       </c>
       <c r="D81" t="n">
-        <v>2374</v>
+        <v>6744</v>
       </c>
       <c r="E81" t="n">
-        <v>2983</v>
+        <v>8136</v>
       </c>
       <c r="J81" s="10" t="n"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>한솔케미칼</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>078350</t>
-        </is>
+          <t>014680</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1889</v>
+      </c>
+      <c r="D82" t="n">
+        <v>2374</v>
+      </c>
+      <c r="E82" t="n">
+        <v>2983</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>082740</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>2442</v>
-      </c>
-      <c r="D83" t="n">
-        <v>3679</v>
-      </c>
-      <c r="E83" t="n">
-        <v>4513</v>
+          <t>078350</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>해성디에스</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>195870</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>897</v>
+        <v>2442</v>
       </c>
       <c r="D84" t="n">
-        <v>1283</v>
+        <v>3679</v>
       </c>
       <c r="E84" t="n">
-        <v>1547</v>
+        <v>4513</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>현대이지웰</t>
+          <t>해성디에스</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>090850</t>
+          <t>195870</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>260</v>
+        <v>897</v>
       </c>
       <c r="D85" t="n">
-        <v>280</v>
+        <v>1283</v>
       </c>
       <c r="E85" t="n">
-        <v>300</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>현대이지웰</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>178320</t>
+          <t>090850</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>635</v>
+        <v>260</v>
       </c>
       <c r="D86" t="n">
-        <v>2904</v>
+        <v>280</v>
       </c>
       <c r="E86" t="n">
-        <v>3492</v>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>한중엔시에스</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>107640</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>-22</v>
+      </c>
+      <c r="D87" t="n">
+        <v>186</v>
+      </c>
+      <c r="E87" t="n">
+        <v>415</v>
       </c>
     </row>
   </sheetData>
